--- a/03_Outputs/all/idx15_vejez_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx15_vejez_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.09973086403021424</v>
+        <v>0.09973086403021428</v>
       </c>
       <c r="D2">
-        <v>0.0313948410746304</v>
+        <v>0.03139484107463043</v>
       </c>
       <c r="E2">
         <v>3.1</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.1117667859729651</v>
+        <v>0.1117667859729652</v>
       </c>
       <c r="D3">
-        <v>0.0351836968140617</v>
+        <v>0.03518369681406175</v>
       </c>
       <c r="E3">
         <v>3.5</v>
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.3265570062931228</v>
+        <v>-0.3265570062931227</v>
       </c>
       <c r="D4">
         <v>0.1027987214797787</v>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.3399163748758204</v>
+        <v>-0.3399163748758203</v>
       </c>
       <c r="D5">
         <v>0.1070041924499704</v>
@@ -483,7 +483,7 @@
         <v>-0.3214616480686797</v>
       </c>
       <c r="D6">
-        <v>0.1011947249313657</v>
+        <v>0.1011947249313658</v>
       </c>
       <c r="E6">
         <v>10.1</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.3199444383984241</v>
+        <v>-0.3199444383984239</v>
       </c>
       <c r="D7">
         <v>0.1007171139436565</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.3397674389857419</v>
+        <v>-0.3397674389857415</v>
       </c>
       <c r="D8">
-        <v>0.1069573080812768</v>
+        <v>0.1069573080812767</v>
       </c>
       <c r="E8">
         <v>10.7</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.3227825222717797</v>
+        <v>-0.3227825222717792</v>
       </c>
       <c r="D9">
-        <v>0.1016105303702251</v>
+        <v>0.101610530370225</v>
       </c>
       <c r="E9">
         <v>10.2</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.3240232980672933</v>
+        <v>-0.324023298067293</v>
       </c>
       <c r="D10">
-        <v>0.102001121179682</v>
+        <v>0.1020011211796819</v>
       </c>
       <c r="E10">
         <v>10.2</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.3433343390301468</v>
+        <v>-0.3433343390301467</v>
       </c>
       <c r="D11">
         <v>0.1080801526601552</v>
@@ -609,7 +609,7 @@
         <v>-0.3273793669084304</v>
       </c>
       <c r="D12">
-        <v>0.1030575970151976</v>
+        <v>0.1030575970151977</v>
       </c>
       <c r="E12">
         <v>10.3</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.6848562294461202</v>
+        <v>-0.6848562294461197</v>
       </c>
       <c r="D13">
-        <v>0.3349745480735648</v>
+        <v>0.3349745480735647</v>
       </c>
       <c r="E13">
         <v>33.5</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.6756794671073892</v>
+        <v>-0.6756794671073889</v>
       </c>
       <c r="D14">
         <v>0.3304860413110856</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.1303970310628328</v>
+        <v>-0.1303970310628327</v>
       </c>
       <c r="D15">
-        <v>0.06377935203383213</v>
+        <v>0.0637793520338321</v>
       </c>
       <c r="E15">
         <v>6.4</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.08540437522493255</v>
+        <v>-0.08540437522493251</v>
       </c>
       <c r="D16">
         <v>0.04177269734059948</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.1634979729208387</v>
+        <v>-0.1634979729208386</v>
       </c>
       <c r="D17">
         <v>0.07996957205805866</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.06925585190411471</v>
+        <v>-0.06925585190411437</v>
       </c>
       <c r="D18">
-        <v>0.03387418657459359</v>
+        <v>0.03387418657459345</v>
       </c>
       <c r="E18">
         <v>3.4</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.04746383737327154</v>
+        <v>0.04746383737327162</v>
       </c>
       <c r="D19">
-        <v>0.02321535059527358</v>
+        <v>0.02321535059527364</v>
       </c>
       <c r="E19">
         <v>2.3</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.1059546474487312</v>
+        <v>-0.1059546474487309</v>
       </c>
       <c r="D20">
-        <v>0.05182417654890426</v>
+        <v>0.05182417654890416</v>
       </c>
       <c r="E20">
         <v>5.2</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.07099330611955942</v>
+        <v>0.0709933061195597</v>
       </c>
       <c r="D21">
-        <v>0.03472400426711542</v>
+        <v>0.03472400426711558</v>
       </c>
       <c r="E21">
         <v>3.5</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.008978403917360468</v>
+        <v>-0.00897840391736035</v>
       </c>
       <c r="D22">
-        <v>0.004391486366521192</v>
+        <v>0.004391486366521137</v>
       </c>
       <c r="E22">
         <v>0.4</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.002021163946228755</v>
+        <v>0.002021163946228727</v>
       </c>
       <c r="D23">
-        <v>0.0009885848304513742</v>
+        <v>0.0009885848304513607</v>
       </c>
       <c r="E23">
         <v>0.1</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.06674126946168892</v>
+        <v>-0.06674126946168935</v>
       </c>
       <c r="D24">
-        <v>0.02416042494444916</v>
+        <v>0.02416042494444931</v>
       </c>
       <c r="E24">
         <v>2.4</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.1323257723475854</v>
+        <v>-0.1323257723475851</v>
       </c>
       <c r="D25">
-        <v>0.04790209890831165</v>
+        <v>0.04790209890831154</v>
       </c>
       <c r="E25">
         <v>4.8</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.3738966360973865</v>
+        <v>0.3738966360973868</v>
       </c>
       <c r="D26">
-        <v>0.1353510606896438</v>
+        <v>0.1353510606896439</v>
       </c>
       <c r="E26">
         <v>13.5</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.02702734265885763</v>
+        <v>-0.02702734265885768</v>
       </c>
       <c r="D27">
-        <v>0.009783932625555944</v>
+        <v>0.00978393262555596</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.3275897200620355</v>
+        <v>0.3275897200620357</v>
       </c>
       <c r="D28">
         <v>0.1185878978324671</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.4620623786981107</v>
+        <v>-0.4620623786981105</v>
       </c>
       <c r="D29">
-        <v>0.1672671723242773</v>
+        <v>0.1672671723242772</v>
       </c>
       <c r="E29">
         <v>16.7</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.09812111350242665</v>
+        <v>0.09812111350242657</v>
       </c>
       <c r="D30">
-        <v>0.03551996863952318</v>
+        <v>0.03551996863952314</v>
       </c>
       <c r="E30">
         <v>3.6</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.4009970044280377</v>
+        <v>0.4009970044280374</v>
       </c>
       <c r="D31">
-        <v>0.1451614287018296</v>
+        <v>0.1451614287018295</v>
       </c>
       <c r="E31">
         <v>14.5</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.3944094051705765</v>
+        <v>-0.3944094051705772</v>
       </c>
       <c r="D32">
-        <v>0.142776709341414</v>
+        <v>0.1427767093414143</v>
       </c>
       <c r="E32">
         <v>14.3</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.04486388804747229</v>
+        <v>0.04486388804747238</v>
       </c>
       <c r="D33">
-        <v>0.01624078487912679</v>
+        <v>0.01624078487912682</v>
       </c>
       <c r="E33">
         <v>1.6</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.434386644449017</v>
+        <v>-0.4343866444490168</v>
       </c>
       <c r="D34">
-        <v>0.1572485211134013</v>
+        <v>0.1572485211134012</v>
       </c>
       <c r="E34">
         <v>15.7</v>
@@ -1092,7 +1092,7 @@
         <v>0.7158103551942503</v>
       </c>
       <c r="D35">
-        <v>0.4141558961340697</v>
+        <v>0.4141558961340698</v>
       </c>
       <c r="E35">
         <v>41.4</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.6863936987975569</v>
+        <v>-0.6863936987975567</v>
       </c>
       <c r="D36">
-        <v>0.3971359108784296</v>
+        <v>0.3971359108784297</v>
       </c>
       <c r="E36">
         <v>39.7</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.01913703977081288</v>
+        <v>-0.01913703977081278</v>
       </c>
       <c r="D37">
-        <v>0.01107237105208338</v>
+        <v>0.01107237105208333</v>
       </c>
       <c r="E37">
         <v>1.1</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.05129824279763</v>
+        <v>-0.05129824279763021</v>
       </c>
       <c r="D38">
-        <v>0.02968030507213064</v>
+        <v>0.02968030507213076</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -1176,7 +1176,7 @@
         <v>-0.06972033089627964</v>
       </c>
       <c r="D39">
-        <v>0.04033901704771608</v>
+        <v>0.04033901704771609</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.03163049488087129</v>
+        <v>-0.03163049488087137</v>
       </c>
       <c r="D40">
-        <v>0.01830087516545692</v>
+        <v>0.01830087516545697</v>
       </c>
       <c r="E40">
         <v>1.8</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.04423577817649273</v>
+        <v>0.04423577817649291</v>
       </c>
       <c r="D41">
-        <v>0.02559408119613136</v>
+        <v>0.02559408119613147</v>
       </c>
       <c r="E41">
         <v>2.6</v>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.01062066423544398</v>
+        <v>0.01062066423544421</v>
       </c>
       <c r="D42">
-        <v>0.006144938644783518</v>
+        <v>0.006144938644783652</v>
       </c>
       <c r="E42">
         <v>0.6</v>
@@ -1260,7 +1260,7 @@
         <v>0.07055657119032693</v>
       </c>
       <c r="D43">
-        <v>0.04082285169169882</v>
+        <v>0.04082285169169883</v>
       </c>
       <c r="E43">
         <v>4.1</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.005731690748194278</v>
+        <v>0.005731690748194268</v>
       </c>
       <c r="D44">
-        <v>0.003316260376727259</v>
+        <v>0.003316260376727254</v>
       </c>
       <c r="E44">
         <v>0.3</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.0232248207534362</v>
+        <v>0.02322482075343565</v>
       </c>
       <c r="D45">
-        <v>0.01343749274077248</v>
+        <v>0.01343749274077217</v>
       </c>
       <c r="E45">
         <v>1.3</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.01924816627717561</v>
+        <v>0.0192481662771756</v>
       </c>
       <c r="D46">
-        <v>0.007242795861812717</v>
+        <v>0.00724279586181271</v>
       </c>
       <c r="E46">
         <v>0.7</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.1859220860047027</v>
+        <v>0.1859220860047031</v>
       </c>
       <c r="D47">
-        <v>0.06995968840581121</v>
+        <v>0.06995968840581133</v>
       </c>
       <c r="E47">
         <v>7</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>9.235458816224331E-06</v>
+        <v>9.235458816064801E-06</v>
       </c>
       <c r="D48">
-        <v>3.475164435555082E-06</v>
+        <v>3.475164435495052E-06</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.3646572324232835</v>
+        <v>-0.3646572324232829</v>
       </c>
       <c r="D49">
-        <v>0.1372150393935076</v>
+        <v>0.1372150393935073</v>
       </c>
       <c r="E49">
         <v>13.7</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.5214640214091512</v>
+        <v>-0.5214640214091522</v>
       </c>
       <c r="D50">
-        <v>0.1962190788441493</v>
+        <v>0.1962190788441497</v>
       </c>
       <c r="E50">
         <v>19.6</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.3103673966613933</v>
+        <v>-0.3103673966613929</v>
       </c>
       <c r="D51">
-        <v>0.1167865896319853</v>
+        <v>0.1167865896319851</v>
       </c>
       <c r="E51">
         <v>11.7</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.3920112670726053</v>
+        <v>0.3920112670726068</v>
       </c>
       <c r="D52">
-        <v>0.147507951773266</v>
+        <v>0.1475079517732665</v>
       </c>
       <c r="E52">
         <v>14.8</v>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.4120126855000404</v>
+        <v>0.4120126855000406</v>
       </c>
       <c r="D53">
         <v>0.1550341851053416</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.3702002667018955</v>
+        <v>0.370200266701894</v>
       </c>
       <c r="D54">
-        <v>0.1393007999359351</v>
+        <v>0.1393007999359345</v>
       </c>
       <c r="E54">
         <v>13.9</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.04434086808771773</v>
+        <v>0.04434086808771912</v>
       </c>
       <c r="D55">
-        <v>0.01668480265965522</v>
+        <v>0.01668480265965573</v>
       </c>
       <c r="E55">
         <v>1.7</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.03732701003827459</v>
+        <v>0.03732701003827385</v>
       </c>
       <c r="D56">
-        <v>0.01404559322410047</v>
+        <v>0.01404559322410019</v>
       </c>
       <c r="E56">
         <v>1.4</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C57">
-        <v>-0.003069649793732866</v>
+        <v>-0.003069649793732519</v>
       </c>
       <c r="D57">
-        <v>0.001204103200348568</v>
+        <v>0.001204103200348434</v>
       </c>
       <c r="E57">
         <v>0.1</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.02651391136074657</v>
+        <v>0.02651391136074742</v>
       </c>
       <c r="D58">
-        <v>0.01040036736060696</v>
+        <v>0.01040036736060731</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.08217096360146076</v>
+        <v>0.08217096360145999</v>
       </c>
       <c r="D59">
-        <v>0.03223244568492786</v>
+        <v>0.0322324456849276</v>
       </c>
       <c r="E59">
         <v>3.2</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>-0.1762749801218864</v>
+        <v>-0.1762749801218857</v>
       </c>
       <c r="D60">
-        <v>0.06914575992984261</v>
+        <v>0.06914575992984244</v>
       </c>
       <c r="E60">
         <v>6.9</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C61">
-        <v>0.49460710527626</v>
+        <v>0.4946071052762583</v>
       </c>
       <c r="D61">
-        <v>0.1940149653534431</v>
+        <v>0.1940149653534427</v>
       </c>
       <c r="E61">
         <v>19.4</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.4480541948146118</v>
+        <v>-0.4480541948146147</v>
       </c>
       <c r="D62">
-        <v>0.1757540847191589</v>
+        <v>0.1757540847191603</v>
       </c>
       <c r="E62">
         <v>17.6</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>-0.194890804632259</v>
+        <v>-0.194890804632256</v>
       </c>
       <c r="D63">
-        <v>0.07644801763879402</v>
+        <v>0.07644801763879296</v>
       </c>
       <c r="E63">
         <v>7.6</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>-0.2352018358079171</v>
+        <v>-0.2352018358079183</v>
       </c>
       <c r="D64">
-        <v>0.09226045388056321</v>
+        <v>0.09226045388056381</v>
       </c>
       <c r="E64">
         <v>9.199999999999999</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.6166301359455756</v>
+        <v>0.6166301359455766</v>
       </c>
       <c r="D65">
-        <v>0.2418798136645207</v>
+        <v>0.2418798136645215</v>
       </c>
       <c r="E65">
         <v>24.2</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>-0.1887336530914403</v>
+        <v>-0.1887336530914383</v>
       </c>
       <c r="D66">
-        <v>0.07403280861707848</v>
+        <v>0.07403280861707778</v>
       </c>
       <c r="E66">
         <v>7.4</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.08317726933771598</v>
+        <v>0.08317726933771527</v>
       </c>
       <c r="D67">
-        <v>0.0326271799507154</v>
+        <v>0.03262717995071517</v>
       </c>
       <c r="E67">
         <v>3.3</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.06129504416821676</v>
+        <v>0.06129504416821665</v>
       </c>
       <c r="D68">
-        <v>0.02291073471214718</v>
+        <v>0.02291073471214712</v>
       </c>
       <c r="E68">
         <v>2.3</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.08200039485602624</v>
+        <v>0.08200039485602573</v>
       </c>
       <c r="D69">
-        <v>0.03064993782665206</v>
+        <v>0.03064993782665185</v>
       </c>
       <c r="E69">
         <v>3.1</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.2486781056733249</v>
+        <v>-0.2486781056733254</v>
       </c>
       <c r="D70">
-        <v>0.0929503875087362</v>
+        <v>0.09295038750873633</v>
       </c>
       <c r="E70">
         <v>9.300000000000001</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.3325221167456633</v>
+        <v>0.332522116745665</v>
       </c>
       <c r="D71">
-        <v>0.1242894283879454</v>
+        <v>0.1242894283879459</v>
       </c>
       <c r="E71">
         <v>12.4</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.003901561979506176</v>
+        <v>0.003901561979504867</v>
       </c>
       <c r="D72">
-        <v>0.001458317759428517</v>
+        <v>0.001458317759428026</v>
       </c>
       <c r="E72">
         <v>0.1</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.3497993002024717</v>
+        <v>-0.3497993002024699</v>
       </c>
       <c r="D73">
-        <v>0.1307472582520649</v>
+        <v>0.1307472582520641</v>
       </c>
       <c r="E73">
         <v>13.1</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.4831156485559023</v>
+        <v>0.4831156485559022</v>
       </c>
       <c r="D74">
-        <v>0.1805779669393005</v>
+        <v>0.1805779669393003</v>
       </c>
       <c r="E74">
         <v>18.1</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.4874570817487703</v>
+        <v>-0.4874570817487694</v>
       </c>
       <c r="D75">
-        <v>0.182200698850209</v>
+        <v>0.1822006988502085</v>
       </c>
       <c r="E75">
         <v>18.2</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>-0.007402211457619932</v>
+        <v>-0.007402211457623738</v>
       </c>
       <c r="D76">
-        <v>0.002766783274082114</v>
+        <v>0.002766783274083535</v>
       </c>
       <c r="E76">
         <v>0.3</v>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.4359981457885223</v>
+        <v>0.4359981457885228</v>
       </c>
       <c r="D77">
         <v>0.1629664843006755</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>-0.1832157458775138</v>
+        <v>-0.1832157458775133</v>
       </c>
       <c r="D78">
-        <v>0.06848200218875888</v>
+        <v>0.06848200218875865</v>
       </c>
       <c r="E78">
         <v>6.8</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.006052522317535537</v>
+        <v>0.006052522317535495</v>
       </c>
       <c r="D79">
-        <v>0.002563373905376745</v>
+        <v>0.002563373905376726</v>
       </c>
       <c r="E79">
         <v>0.3</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.0168644173344401</v>
+        <v>0.01686441733444032</v>
       </c>
       <c r="D80">
-        <v>0.007142444927338868</v>
+        <v>0.007142444927338957</v>
       </c>
       <c r="E80">
         <v>0.7</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="C81">
-        <v>0.002358033007236909</v>
+        <v>0.002358033007237624</v>
       </c>
       <c r="D81">
-        <v>0.0009986779001633407</v>
+        <v>0.0009986779001636427</v>
       </c>
       <c r="E81">
         <v>0.1</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.671651411425921</v>
+        <v>-0.6716514114259211</v>
       </c>
       <c r="D82">
         <v>0.2844588770157074</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="C83">
-        <v>0.3386375229786397</v>
+        <v>0.3386375229786394</v>
       </c>
       <c r="D83">
-        <v>0.1434203038409145</v>
+        <v>0.1434203038409143</v>
       </c>
       <c r="E83">
         <v>14.3</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="C84">
-        <v>0.2988740656140524</v>
+        <v>0.2988740656140528</v>
       </c>
       <c r="D84">
-        <v>0.1265796209572458</v>
+        <v>0.1265796209572459</v>
       </c>
       <c r="E84">
         <v>12.7</v>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.4935188536014331</v>
+        <v>0.4935188536014336</v>
       </c>
       <c r="D85">
-        <v>0.2090158920138392</v>
+        <v>0.2090158920138393</v>
       </c>
       <c r="E85">
         <v>20.9</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C86">
-        <v>-0.2356487210882982</v>
+        <v>-0.2356487210882991</v>
       </c>
       <c r="D86">
-        <v>0.09980232220260614</v>
+        <v>0.09980232220260651</v>
       </c>
       <c r="E86">
         <v>10</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.2023122271276397</v>
+        <v>-0.2023122271276393</v>
       </c>
       <c r="D87">
-        <v>0.08568359711043723</v>
+        <v>0.08568359711043701</v>
       </c>
       <c r="E87">
         <v>8.6</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C88">
-        <v>-0.04726511408021922</v>
+        <v>-0.04726511408021926</v>
       </c>
       <c r="D88">
-        <v>0.02001779650062026</v>
+        <v>0.02001779650062027</v>
       </c>
       <c r="E88">
         <v>2</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.04797180089076375</v>
+        <v>0.04797180089076324</v>
       </c>
       <c r="D89">
-        <v>0.0203170936257503</v>
+        <v>0.02031709362575007</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="C90">
-        <v>0.00339083420330035</v>
+        <v>0.003390834203300404</v>
       </c>
       <c r="D90">
-        <v>0.00173163009733633</v>
+        <v>0.001731630097336391</v>
       </c>
       <c r="E90">
         <v>0.2</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="C91">
-        <v>-0.004317040279266967</v>
+        <v>-0.004317040279266745</v>
       </c>
       <c r="D91">
-        <v>0.002204624712029825</v>
+        <v>0.002204624712029755</v>
       </c>
       <c r="E91">
         <v>0.2</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="C92">
-        <v>-0.8074350926594036</v>
+        <v>-0.8074350926594045</v>
       </c>
       <c r="D92">
-        <v>0.4123406879444896</v>
+        <v>0.4123406879444981</v>
       </c>
       <c r="E92">
         <v>41.2</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.07035222638030086</v>
+        <v>0.07035222638029959</v>
       </c>
       <c r="D93">
-        <v>0.03592745186307686</v>
+        <v>0.03592745186307691</v>
       </c>
       <c r="E93">
         <v>3.6</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="C94">
-        <v>0.3508187580736175</v>
+        <v>0.3508187580736186</v>
       </c>
       <c r="D94">
-        <v>0.17915600815845</v>
+        <v>0.179156008158454</v>
       </c>
       <c r="E94">
         <v>17.9</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="C95">
-        <v>0.01636794470898126</v>
+        <v>0.0163679447089716</v>
       </c>
       <c r="D95">
-        <v>0.00835877662848334</v>
+        <v>0.008358776628478568</v>
       </c>
       <c r="E95">
         <v>0.8</v>
@@ -2373,7 +2373,7 @@
         <v>0.06915451710110897</v>
       </c>
       <c r="D96">
-        <v>0.03531580608172635</v>
+        <v>0.03531580608172704</v>
       </c>
       <c r="E96">
         <v>3.5</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.447157213465707</v>
+        <v>0.4471572134657079</v>
       </c>
       <c r="D97">
-        <v>0.2283540989189668</v>
+        <v>0.2283540989189718</v>
       </c>
       <c r="E97">
         <v>22.8</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C98">
-        <v>0.02667139671849318</v>
+        <v>0.0266713967184833</v>
       </c>
       <c r="D98">
-        <v>0.0136205401168797</v>
+        <v>0.01362054011687492</v>
       </c>
       <c r="E98">
         <v>1.4</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="C99">
-        <v>-0.1044853288521752</v>
+        <v>-0.1044853288521743</v>
       </c>
       <c r="D99">
-        <v>0.05335853342354776</v>
+        <v>0.05335853342354831</v>
       </c>
       <c r="E99">
         <v>5.3</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.05802432268963872</v>
+        <v>-0.05802432268961925</v>
       </c>
       <c r="D100">
-        <v>0.02963184205501356</v>
+        <v>0.0296318420550042</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>-0.001228420202874897</v>
+        <v>-0.001228420202874834</v>
       </c>
       <c r="D101">
-        <v>0.0005986852203993863</v>
+        <v>0.0005986852203993673</v>
       </c>
       <c r="E101">
         <v>0.1</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.00233270982856205</v>
+        <v>0.002332709828561653</v>
       </c>
       <c r="D102">
-        <v>0.001136873925202541</v>
+        <v>0.001136873925202369</v>
       </c>
       <c r="E102">
         <v>0.1</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.07365656365626735</v>
+        <v>-0.0736565636562473</v>
       </c>
       <c r="D103">
-        <v>0.03589740379001626</v>
+        <v>0.03589740379000717</v>
       </c>
       <c r="E103">
         <v>3.6</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="C104">
-        <v>-0.06669572715716625</v>
+        <v>-0.06669572715716678</v>
       </c>
       <c r="D104">
-        <v>0.03250495719570308</v>
+        <v>0.03250495719570395</v>
       </c>
       <c r="E104">
         <v>3.3</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.03663586762032502</v>
+        <v>0.03663586762031613</v>
       </c>
       <c r="D105">
-        <v>0.01785492653854598</v>
+        <v>0.01785492653854199</v>
       </c>
       <c r="E105">
         <v>1.8</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.4024617197211136</v>
+        <v>-0.4024617197211137</v>
       </c>
       <c r="D106">
-        <v>0.1961445137499821</v>
+        <v>0.1961445137499859</v>
       </c>
       <c r="E106">
         <v>19.6</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.08294520078684303</v>
+        <v>-0.08294520078684223</v>
       </c>
       <c r="D107">
-        <v>0.04042433175384669</v>
+        <v>0.04042433175384706</v>
       </c>
       <c r="E107">
         <v>4</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.03813287587928639</v>
+        <v>0.0381328758792757</v>
       </c>
       <c r="D108">
-        <v>0.01858451134784699</v>
+        <v>0.01858451134784213</v>
       </c>
       <c r="E108">
         <v>1.9</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.4050633809762632</v>
+        <v>-0.4050633809762643</v>
       </c>
       <c r="D109">
-        <v>0.1974124643570289</v>
+        <v>0.1974124643570332</v>
       </c>
       <c r="E109">
         <v>19.7</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="C110">
-        <v>0.1472877766231165</v>
+        <v>0.1472877766231139</v>
       </c>
       <c r="D110">
-        <v>0.07178245261953439</v>
+        <v>0.07178245261953448</v>
       </c>
       <c r="E110">
         <v>7.2</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="C111">
-        <v>0.7954230089165898</v>
+        <v>0.7954230089165922</v>
       </c>
       <c r="D111">
-        <v>0.3876588795018939</v>
+        <v>0.3876588795019024</v>
       </c>
       <c r="E111">
         <v>38.8</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.0004485557780547358</v>
+        <v>0.000448555778054656</v>
       </c>
       <c r="D112">
-        <v>0.000210813416794554</v>
+        <v>0.0002108134167945167</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.004057369331852991</v>
+        <v>-0.004057369331853137</v>
       </c>
       <c r="D113">
-        <v>0.00190689304183033</v>
+        <v>0.001906893041830401</v>
       </c>
       <c r="E113">
         <v>0.2</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C114">
-        <v>0.1010795183099391</v>
+        <v>0.101079518309942</v>
       </c>
       <c r="D114">
-        <v>0.04750561616946931</v>
+        <v>0.04750561616947072</v>
       </c>
       <c r="E114">
         <v>4.8</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.3723826871239835</v>
+        <v>0.3723826871239834</v>
       </c>
       <c r="D115">
-        <v>0.1750133884534752</v>
+        <v>0.1750133884534755</v>
       </c>
       <c r="E115">
         <v>17.5</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.04568781303118552</v>
+        <v>-0.04568781303118688</v>
       </c>
       <c r="D116">
-        <v>0.021472477765741</v>
+        <v>0.02147247776574166</v>
       </c>
       <c r="E116">
         <v>2.1</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="C117">
-        <v>-0.0856035508922476</v>
+        <v>-0.08560355089224546</v>
       </c>
       <c r="D117">
-        <v>0.04023218055868865</v>
+        <v>0.04023218055868771</v>
       </c>
       <c r="E117">
         <v>4</v>
@@ -2835,7 +2835,7 @@
         <v>0.4363961652102813</v>
       </c>
       <c r="D118">
-        <v>0.205098610172833</v>
+        <v>0.2050986101728333</v>
       </c>
       <c r="E118">
         <v>20.5</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.06364658102076631</v>
+        <v>-0.06364658102076737</v>
       </c>
       <c r="D119">
-        <v>0.02991278647767604</v>
+        <v>0.02991278647767658</v>
       </c>
       <c r="E119">
         <v>3</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.07986329668630721</v>
+        <v>-0.07986329668630508</v>
       </c>
       <c r="D120">
-        <v>0.03753436088580075</v>
+        <v>0.03753436088579981</v>
       </c>
       <c r="E120">
         <v>3.8</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.7857923056102507</v>
+        <v>-0.785792305610251</v>
       </c>
       <c r="D121">
-        <v>0.369308721325518</v>
+        <v>0.3693087213255186</v>
       </c>
       <c r="E121">
         <v>36.9</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C122">
-        <v>0.1527804427133466</v>
+        <v>0.1527804427133424</v>
       </c>
       <c r="D122">
-        <v>0.07180415173217311</v>
+        <v>0.07180415173217125</v>
       </c>
       <c r="E122">
         <v>7.2</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7634457443735987</v>
+        <v>0.7634457443735988</v>
       </c>
     </row>
     <row r="3">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1552456228630448</v>
+        <v>0.1552456228630446</v>
       </c>
     </row>
     <row r="4">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.04725484079429664</v>
+        <v>0.04725484079429673</v>
       </c>
     </row>
     <row r="5">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.02005528177882338</v>
+        <v>0.02005528177882341</v>
       </c>
     </row>
     <row r="6">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.005616305015209244</v>
+        <v>0.005616305015209256</v>
       </c>
     </row>
     <row r="7">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.004548378167322994</v>
+        <v>0.004548378167323005</v>
       </c>
     </row>
     <row r="8">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.003319396744102281</v>
+        <v>0.003319396744102278</v>
       </c>
     </row>
     <row r="9">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0004941305707976454</v>
+        <v>0.0004941305707976465</v>
       </c>
     </row>
     <row r="10">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>9.765947959895601E-06</v>
+        <v>9.765947959895576E-06</v>
       </c>
     </row>
     <row r="11">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>8.025482342619056E-06</v>
+        <v>8.025482342618915E-06</v>
       </c>
     </row>
     <row r="12">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.508262501741694E-06</v>
+        <v>2.508262501741735E-06</v>
       </c>
     </row>
   </sheetData>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.3433343390301468</v>
+        <v>-0.3433343390301467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.3399163748758204</v>
+        <v>-0.3399163748758203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.3397674389857419</v>
+        <v>-0.3397674389857415</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.3265570062931228</v>
+        <v>-0.3265570062931227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.3240232980672933</v>
+        <v>-0.324023298067293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3227825222717797</v>
+        <v>-0.3227825222717792</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.3199444383984241</v>
+        <v>-0.3199444383984239</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.1117667859729651</v>
+        <v>0.1117667859729652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.6848562294461202</v>
+        <v>-0.6848562294461197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.6756794671073892</v>
+        <v>-0.6756794671073889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.1634979729208387</v>
+        <v>-0.1634979729208386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.1303970310628328</v>
+        <v>-0.1303970310628327</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.1059546474487312</v>
+        <v>-0.1059546474487309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.08540437522493255</v>
+        <v>-0.08540437522493251</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.07099330611955942</v>
+        <v>0.0709933061195597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.06925585190411471</v>
+        <v>-0.06925585190411437</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.04746383737327154</v>
+        <v>0.04746383737327162</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.008978403917360468</v>
+        <v>-0.00897840391736035</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/03_Outputs/all/idx15_vejez_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx15_vejez_loadings_y_tops.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -396,13 +396,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2236985956981443</v>
+        <v>0.1218796553531745</v>
       </c>
       <c r="D2">
-        <v>0.09586640788766528</v>
+        <v>0.04289685147295035</v>
       </c>
       <c r="E2">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -417,19 +417,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.2416496449724561</v>
+        <v>0.1348009920480477</v>
       </c>
       <c r="D3">
-        <v>0.1035593601226668</v>
+        <v>0.04744465446292265</v>
       </c>
       <c r="E3">
-        <v>10.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.4953225160048044</v>
+        <v>-0.3716514935672572</v>
       </c>
       <c r="D4">
-        <v>0.2122712939125308</v>
+        <v>0.1308067279404196</v>
       </c>
       <c r="E4">
-        <v>21.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.5137180503361372</v>
+        <v>-0.3716514935672572</v>
       </c>
       <c r="D5">
-        <v>0.2201547309632432</v>
+        <v>0.1308067279404196</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (H)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.5111609600233182</v>
+        <v>-0.3938790855652767</v>
       </c>
       <c r="D6">
-        <v>0.2190588856264889</v>
+        <v>0.1386299672643035</v>
       </c>
       <c r="E6">
-        <v>21.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mortalidad IAM x100k</t>
+          <t>Índice envejecimiento H (rural)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -501,103 +501,103 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.3478911183300195</v>
+        <v>-0.3767323395843357</v>
       </c>
       <c r="D7">
-        <v>0.149089321487405</v>
+        <v>0.1325949861720332</v>
       </c>
       <c r="E7">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (H)</t>
+          <t>Índice envejecimiento (M)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C8">
-        <v>-0.6491140839641749</v>
+        <v>-0.3937444483050733</v>
       </c>
       <c r="D8">
-        <v>0.3264257979325651</v>
+        <v>0.1385825802370188</v>
       </c>
       <c r="E8">
-        <v>32.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (M)</t>
+          <t>Índice envejecimiento</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C9">
-        <v>-0.6364962040834916</v>
+        <v>-0.3978872158482284</v>
       </c>
       <c r="D9">
-        <v>0.3200805319615734</v>
+        <v>0.1400406716918291</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>Índice envejecimiento (rural)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C10">
-        <v>-0.1845318536964783</v>
+        <v>-0.3834588968498912</v>
       </c>
       <c r="D10">
-        <v>0.09279718168951757</v>
+        <v>0.1349624701225637</v>
       </c>
       <c r="E10">
-        <v>9.300000000000001</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>Mortalidad IAM x100k</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C11">
-        <v>-0.05508755646415955</v>
+        <v>-0.2671920041258692</v>
       </c>
       <c r="D11">
-        <v>0.02770237161571271</v>
+        <v>0.09404109063595918</v>
       </c>
       <c r="E11">
-        <v>2.8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>% ocupados cotizan pensión (H)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.1110287780636005</v>
+        <v>-0.6763207378896414</v>
       </c>
       <c r="D12">
-        <v>0.05583403344378631</v>
+        <v>0.3438105345455761</v>
       </c>
       <c r="E12">
-        <v>5.6</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mortalidad IAM x100k</t>
+          <t>% ocupados cotizan pensión (M)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -627,55 +627,55 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.3522917182144775</v>
+        <v>-0.6685620940152283</v>
       </c>
       <c r="D13">
-        <v>0.1771600833568449</v>
+        <v>0.3398663948077731</v>
       </c>
       <c r="E13">
-        <v>17.7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (H)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C14">
-        <v>-0.1832811660996181</v>
+        <v>-0.1114790985972182</v>
       </c>
       <c r="D14">
-        <v>0.09393261660673118</v>
+        <v>0.05667087571344392</v>
       </c>
       <c r="E14">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (M)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C15">
-        <v>-0.1495187996820083</v>
+        <v>-0.1114790985972182</v>
       </c>
       <c r="D15">
-        <v>0.07662921611048165</v>
+        <v>0.05667087571344392</v>
       </c>
       <c r="E15">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="16">
@@ -686,311 +686,311 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C16">
-        <v>-0.2830377779131775</v>
+        <v>-0.08654659686999255</v>
       </c>
       <c r="D16">
-        <v>0.1450584347738664</v>
+        <v>0.04399633201522203</v>
       </c>
       <c r="E16">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>Índice envejecimiento H (rural)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C17">
-        <v>-0.2176206621898006</v>
+        <v>-0.09374409652655259</v>
       </c>
       <c r="D17">
-        <v>0.111531799268818</v>
+        <v>0.04765521169416705</v>
       </c>
       <c r="E17">
-        <v>11.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (M)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C18">
-        <v>-0.2491025407002839</v>
+        <v>0.0459131983015012</v>
       </c>
       <c r="D18">
-        <v>0.1276664370339314</v>
+        <v>0.02334017037536405</v>
       </c>
       <c r="E18">
-        <v>12.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mortalidad IAM x100k</t>
+          <t>Índice envejecimiento</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C19">
-        <v>0.8686373987881956</v>
+        <v>-0.01028862453839766</v>
       </c>
       <c r="D19">
-        <v>0.4451814962061715</v>
+        <v>0.005230266209672893</v>
       </c>
       <c r="E19">
-        <v>44.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (H)</t>
+          <t>Índice envejecimiento (rural)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C20">
-        <v>0.7031910391615045</v>
+        <v>-0.02077488092041863</v>
       </c>
       <c r="D20">
-        <v>0.4611725599088453</v>
+        <v>0.01056099941080812</v>
       </c>
       <c r="E20">
-        <v>46.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (M)</t>
+          <t>Mortalidad IAM x100k</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C21">
-        <v>-0.7072760490947851</v>
+        <v>-0.2535027696269961</v>
       </c>
       <c r="D21">
-        <v>0.4638516248901489</v>
+        <v>0.1288692152279728</v>
       </c>
       <c r="E21">
-        <v>46.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>% ocupados cotizan pensión (H)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C22">
-        <v>-0.06358950434353958</v>
+        <v>-0.1503125929423894</v>
       </c>
       <c r="D22">
-        <v>0.04170379437202901</v>
+        <v>0.07669039423839323</v>
       </c>
       <c r="E22">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>% ocupados cotizan pensión (M)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C23">
-        <v>0.0324314404728806</v>
+        <v>-0.1404468535890093</v>
       </c>
       <c r="D23">
-        <v>0.02126945537054059</v>
+        <v>0.07165683433730143</v>
       </c>
       <c r="E23">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C24">
-        <v>-0.005983747241541493</v>
+        <v>-0.1230937063764567</v>
       </c>
       <c r="D24">
-        <v>0.003924310577847662</v>
+        <v>0.06280315365122877</v>
       </c>
       <c r="E24">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mortalidad IAM x100k</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C25">
-        <v>0.01231763755678654</v>
+        <v>-0.1230937063764567</v>
       </c>
       <c r="D25">
-        <v>0.008078254880588583</v>
+        <v>0.06280315365122877</v>
       </c>
       <c r="E25">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (H)</t>
+          <t>Índice envejecimiento (H)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C26">
-        <v>-0.02323234905768351</v>
+        <v>-0.1499815690969649</v>
       </c>
       <c r="D26">
-        <v>0.014381369074758</v>
+        <v>0.076521503869922</v>
       </c>
       <c r="E26">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (M)</t>
+          <t>Índice envejecimiento H (rural)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C27">
-        <v>-0.1177044736422652</v>
+        <v>-0.1360660500790462</v>
       </c>
       <c r="D27">
-        <v>0.07286183041571105</v>
+        <v>0.06942172188475543</v>
       </c>
       <c r="E27">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>Índice envejecimiento (M)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C28">
-        <v>0.7057649924094178</v>
+        <v>-0.07848923409337831</v>
       </c>
       <c r="D28">
-        <v>0.4368850868537896</v>
+        <v>0.04004568205671081</v>
       </c>
       <c r="E28">
-        <v>43.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>Índice envejecimiento</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C29">
-        <v>-0.6955158817086231</v>
+        <v>-0.1110231943899647</v>
       </c>
       <c r="D29">
-        <v>0.4305406468959441</v>
+        <v>0.05664470541490491</v>
       </c>
       <c r="E29">
-        <v>43.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (rural)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C30">
-        <v>-0.05983172982527028</v>
+        <v>-0.1416123151556794</v>
       </c>
       <c r="D30">
-        <v>0.03703724435535898</v>
+        <v>0.0722514598791007</v>
       </c>
       <c r="E30">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="31">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C31">
-        <v>0.01339823601777563</v>
+        <v>0.9289669244664316</v>
       </c>
       <c r="D31">
-        <v>0.008293822404438329</v>
+        <v>0.4739645446676827</v>
       </c>
       <c r="E31">
-        <v>0.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="32">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C32">
-        <v>0.0006919793475195126</v>
+        <v>-0.1725509302047509</v>
       </c>
       <c r="D32">
-        <v>0.0004220863225566139</v>
+        <v>0.0715381685523705</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="33">
@@ -1043,100 +1043,1234 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C33">
-        <v>-0.005329828806959233</v>
+        <v>0.1632907294264285</v>
       </c>
       <c r="D33">
-        <v>0.003251033212262583</v>
+        <v>0.06769896697100354</v>
       </c>
       <c r="E33">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C34">
-        <v>0.3719480700456191</v>
+        <v>-0.5775140630543756</v>
       </c>
       <c r="D34">
-        <v>0.2268769922546832</v>
+        <v>0.2394324871800124</v>
       </c>
       <c r="E34">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C35">
-        <v>0.4482256499015314</v>
+        <v>-0.5775140630543756</v>
       </c>
       <c r="D35">
-        <v>0.2734039923599755</v>
+        <v>0.2394324871800124</v>
       </c>
       <c r="E35">
-        <v>27.3</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (H)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C36">
-        <v>-0.8128464593522396</v>
+        <v>-0.05398369908735721</v>
       </c>
       <c r="D36">
-        <v>0.4958115788585387</v>
+        <v>0.02238118890352686</v>
       </c>
       <c r="E36">
-        <v>49.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PC4</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>0.5459967485952276</v>
+      </c>
+      <c r="D37">
+        <v>0.2263656729274254</v>
+      </c>
+      <c r="E37">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (M)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PC4</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>-0.2380687195848599</v>
+      </c>
+      <c r="D38">
+        <v>0.09870129455981232</v>
+      </c>
+      <c r="E38">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PC4</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>-0.1606571511933721</v>
+      </c>
+      <c r="D39">
+        <v>0.06660710752226755</v>
+      </c>
+      <c r="E39">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PC4</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>0.4753088532780497</v>
+      </c>
+      <c r="D40">
+        <v>0.1970590643579321</v>
+      </c>
+      <c r="E40">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Mortalidad IAM x100k</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PC4</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>0.02464123415603888</v>
+      </c>
+      <c r="D41">
+        <v>0.01021604902564937</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (H)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>0.6865086982565878</v>
+      </c>
+      <c r="D42">
+        <v>0.3618544857530006</v>
+      </c>
+      <c r="E42">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (M)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>-0.6839821079821803</v>
+      </c>
+      <c r="D43">
+        <v>0.360522735657516</v>
+      </c>
+      <c r="E43">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>-0.1588009378837617</v>
+      </c>
+      <c r="D44">
+        <v>0.08370299147112283</v>
+      </c>
+      <c r="E44">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>-0.1588009378837617</v>
+      </c>
+      <c r="D45">
+        <v>0.08370299147112283</v>
+      </c>
+      <c r="E45">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (H)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>-0.05831691298540539</v>
+      </c>
+      <c r="D46">
+        <v>0.03073848388611274</v>
+      </c>
+      <c r="E46">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>0.1090634603615504</v>
+      </c>
+      <c r="D47">
+        <v>0.05748667491583802</v>
+      </c>
+      <c r="E47">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (M)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>-0.02137822468535447</v>
+      </c>
+      <c r="D48">
+        <v>0.0112683299126091</v>
+      </c>
+      <c r="E48">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>-0.03451437938827759</v>
+      </c>
+      <c r="D49">
+        <v>0.01819231575120003</v>
+      </c>
+      <c r="E49">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>0.1365553411033912</v>
+      </c>
+      <c r="D50">
+        <v>0.07197747509577024</v>
+      </c>
+      <c r="E50">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Mortalidad IAM x100k</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PC5</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>0.00807542693820198</v>
+      </c>
+      <c r="D51">
+        <v>0.004256507556830457</v>
+      </c>
+      <c r="E51">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (H)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>PC6</t>
         </is>
       </c>
-      <c r="C37">
-        <v>-0.0003841454000292551</v>
-      </c>
-      <c r="D37">
-        <v>0.0002343169919833706</v>
-      </c>
-      <c r="E37">
+      <c r="C52">
+        <v>-0.06166707892120611</v>
+      </c>
+      <c r="D52">
+        <v>0.02621742934182147</v>
+      </c>
+      <c r="E52">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (M)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>-0.1394362871165467</v>
+      </c>
+      <c r="D53">
+        <v>0.05928059296979095</v>
+      </c>
+      <c r="E53">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>0.5140558474703953</v>
+      </c>
+      <c r="D54">
+        <v>0.2185480988328554</v>
+      </c>
+      <c r="E54">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>0.5140558474703953</v>
+      </c>
+      <c r="D55">
+        <v>0.2185480988328554</v>
+      </c>
+      <c r="E55">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (H)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>0.2282492616746221</v>
+      </c>
+      <c r="D56">
+        <v>0.09703895490044863</v>
+      </c>
+      <c r="E56">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>0.3125439554500397</v>
+      </c>
+      <c r="D57">
+        <v>0.1328763938809987</v>
+      </c>
+      <c r="E57">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (M)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>-0.6853349728865477</v>
+      </c>
+      <c r="D58">
+        <v>0.2913665044859689</v>
+      </c>
+      <c r="E58">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>-0.2796850628164007</v>
+      </c>
+      <c r="D59">
+        <v>0.1189066111226218</v>
+      </c>
+      <c r="E59">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>-0.1213044898415343</v>
+      </c>
+      <c r="D60">
+        <v>0.05157195617015815</v>
+      </c>
+      <c r="E60">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Mortalidad IAM x100k</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PC6</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>0.009863603341108858</v>
+      </c>
+      <c r="D61">
+        <v>0.004193458295336067</v>
+      </c>
+      <c r="E61">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (H)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>0.01642099446938781</v>
+      </c>
+      <c r="D62">
+        <v>0.007789232064859443</v>
+      </c>
+      <c r="E62">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (M)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>-0.03411774195502301</v>
+      </c>
+      <c r="D63">
+        <v>0.0161836123940046</v>
+      </c>
+      <c r="E63">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>-0.4580161579352011</v>
+      </c>
+      <c r="D64">
+        <v>0.2172581051813483</v>
+      </c>
+      <c r="E64">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>-0.4580161579352011</v>
+      </c>
+      <c r="D65">
+        <v>0.2172581051813483</v>
+      </c>
+      <c r="E65">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (H)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>0.6868765604933492</v>
+      </c>
+      <c r="D66">
+        <v>0.3258171080666971</v>
+      </c>
+      <c r="E66">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>0.04333797153120337</v>
+      </c>
+      <c r="D67">
+        <v>0.02055719086356893</v>
+      </c>
+      <c r="E67">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (M)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>-0.1161595445871811</v>
+      </c>
+      <c r="D68">
+        <v>0.05509980842053551</v>
+      </c>
+      <c r="E68">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>0.2722008644063862</v>
+      </c>
+      <c r="D69">
+        <v>0.1291173750206936</v>
+      </c>
+      <c r="E69">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>-0.476977057683561</v>
+      </c>
+      <c r="D70">
+        <v>0.2262521310044394</v>
+      </c>
+      <c r="E70">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mortalidad IAM x100k</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>0.004059140849795714</v>
+      </c>
+      <c r="D71">
+        <v>0.001925436983853288</v>
+      </c>
+      <c r="E71">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (H)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>-3.866169752785449E-05</v>
+      </c>
+      <c r="D72">
+        <v>1.944970155451392E-05</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (M)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>-0.0008487538943515288</v>
+      </c>
+      <c r="D73">
+        <v>0.0004269861644454488</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>0.0377760432608932</v>
+      </c>
+      <c r="D74">
+        <v>0.01900415176559252</v>
+      </c>
+      <c r="E74">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>0.0377760432608932</v>
+      </c>
+      <c r="D75">
+        <v>0.01900415176559252</v>
+      </c>
+      <c r="E75">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (H)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>-0.3672133391506433</v>
+      </c>
+      <c r="D76">
+        <v>0.1847355473248634</v>
+      </c>
+      <c r="E76">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>0.6489228596592564</v>
+      </c>
+      <c r="D77">
+        <v>0.3264563317009292</v>
+      </c>
+      <c r="E77">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (M)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>0.3102467435711058</v>
+      </c>
+      <c r="D78">
+        <v>0.1560771243003588</v>
+      </c>
+      <c r="E78">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>-0.01072464023497499</v>
+      </c>
+      <c r="D79">
+        <v>0.005395289529113733</v>
+      </c>
+      <c r="E79">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>-0.5879444256829973</v>
+      </c>
+      <c r="D80">
+        <v>0.2957796563882276</v>
+      </c>
+      <c r="E80">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Mortalidad IAM x100k</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>-0.02406297867647391</v>
+      </c>
+      <c r="D81">
+        <v>0.01210546312491474</v>
+      </c>
+      <c r="E81">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (H)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>-0.001112672950311675</v>
+      </c>
+      <c r="D82">
+        <v>0.0006665062375883852</v>
+      </c>
+      <c r="E82">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (M)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>0.005049265816980389</v>
+      </c>
+      <c r="D83">
+        <v>0.003024578930688087</v>
+      </c>
+      <c r="E83">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>0.009800090033825006</v>
+      </c>
+      <c r="D84">
+        <v>0.005870387281943438</v>
+      </c>
+      <c r="E84">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>0.009800090033825006</v>
+      </c>
+      <c r="D85">
+        <v>0.005870387281943438</v>
+      </c>
+      <c r="E85">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (H)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>-0.3870615042703761</v>
+      </c>
+      <c r="D86">
+        <v>0.2318551078771941</v>
+      </c>
+      <c r="E86">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>0.01003738899721676</v>
+      </c>
+      <c r="D87">
+        <v>0.006012532589987063</v>
+      </c>
+      <c r="E87">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (M)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>-0.4473621321592177</v>
+      </c>
+      <c r="D88">
+        <v>0.2679760045046812</v>
+      </c>
+      <c r="E88">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>0.8061139699252243</v>
+      </c>
+      <c r="D89">
+        <v>0.482873236930761</v>
+      </c>
+      <c r="E89">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>0.002687611096494377</v>
+      </c>
+      <c r="D90">
+        <v>0.001609915617633638</v>
+      </c>
+      <c r="E90">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mortalidad IAM x100k</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>-0.0001865233580375967</v>
+      </c>
+      <c r="D91">
+        <v>0.0001117300295232004</v>
+      </c>
+      <c r="E91">
         <v>0</v>
       </c>
     </row>
@@ -1147,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1169,7 +2303,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6061991634649424</v>
+        <v>0.6891294412979869</v>
       </c>
     </row>
     <row r="3">
@@ -1179,7 +2313,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2743378463586879</v>
+        <v>0.1908814095148781</v>
       </c>
     </row>
     <row r="4">
@@ -1189,7 +2323,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0785192499586413</v>
+        <v>0.05750355184342943</v>
       </c>
     </row>
     <row r="5">
@@ -1199,7 +2333,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.03660399667582158</v>
+        <v>0.03220637692349819</v>
       </c>
     </row>
     <row r="6">
@@ -1209,7 +2343,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.004332742583562985</v>
+        <v>0.02395931985424129</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +2353,37 @@
         </is>
       </c>
       <c r="B7">
-        <v>7.00095834386312E-06</v>
+        <v>0.003343493198429483</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PC7</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.00215119852818674</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PC8</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.0008217142568240591</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PC9</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>3.494582525851946E-06</v>
       </c>
     </row>
   </sheetData>
@@ -1229,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1252,11 +2416,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (M)</t>
+          <t>Índice envejecimiento</t>
         </is>
       </c>
       <c r="B2">
-        <v>-0.5137180503361372</v>
+        <v>-0.3978872158482284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1267,11 +2431,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (H)</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.5111609600233182</v>
+        <v>-0.3938790855652767</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1282,11 +2446,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>Índice envejecimiento (M)</t>
         </is>
       </c>
       <c r="B4">
-        <v>-0.4953225160048044</v>
+        <v>-0.3937444483050733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1297,11 +2461,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mortalidad IAM x100k</t>
+          <t>Índice envejecimiento (rural)</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.3478911183300195</v>
+        <v>-0.3834588968498912</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1312,28 +2476,88 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>% ocupados cotizan pensión (M)</t>
+          <t>Índice envejecimiento H (rural)</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.2416496449724561</v>
+        <v>-0.3767323395843357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>-0.3716514935672572</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (urb.)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>-0.3716514935672572</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mortalidad IAM x100k</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>-0.2671920041258692</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>% ocupados cotizan pensión (M)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.1348009920480477</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>% ocupados cotizan pensión (H)</t>
         </is>
       </c>
-      <c r="B7">
-        <v>0.2236985956981443</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B11">
+        <v>0.1218796553531745</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>+</t>
         </is>
@@ -1346,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1373,7 +2597,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.6491140839641749</v>
+        <v>-0.6763207378896414</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1388,7 +2612,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.6364962040834916</v>
+        <v>-0.6685620940152283</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1403,7 +2627,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.3522917182144775</v>
+        <v>-0.2535027696269961</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1414,11 +2638,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Índice envejecimiento (H)</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.1845318536964783</v>
+        <v>-0.1114790985972182</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1429,11 +2653,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Índice envejecimiento</t>
+          <t>Índice envejecimiento (urb.)</t>
         </is>
       </c>
       <c r="B6">
-        <v>-0.1110287780636005</v>
+        <v>-0.1114790985972182</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1444,13 +2668,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Índice envejecimiento H (rural)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>-0.09374409652655259</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (H)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>-0.08654659686999255</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Índice envejecimiento (M)</t>
         </is>
       </c>
-      <c r="B7">
-        <v>-0.05508755646415955</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B9">
+        <v>0.0459131983015012</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento (rural)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>-0.02077488092041863</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Índice envejecimiento</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>-0.01028862453839766</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
